--- a/src/models/prediction/one_day_output.xlsx
+++ b/src/models/prediction/one_day_output.xlsx
@@ -508,7 +508,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>129.0590667724609</v>
+        <v>128.4206848144531</v>
       </c>
     </row>
     <row r="3">
@@ -545,7 +545,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>130.990478515625</v>
+        <v>131.7485198974609</v>
       </c>
     </row>
     <row r="4">
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>128.7005157470703</v>
+        <v>129.5088653564453</v>
       </c>
     </row>
     <row r="5">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>127.3258666992188</v>
+        <v>127.6254425048828</v>
       </c>
     </row>
     <row r="6">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>124.8476257324219</v>
+        <v>125.798095703125</v>
       </c>
     </row>
     <row r="7">
@@ -693,7 +693,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>123.0583877563477</v>
+        <v>123.3608016967773</v>
       </c>
     </row>
     <row r="8">
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>122.4418182373047</v>
+        <v>122.9794235229492</v>
       </c>
     </row>
     <row r="9">
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>123.663330078125</v>
+        <v>124.0448226928711</v>
       </c>
     </row>
     <row r="10">
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>123.6173629760742</v>
+        <v>124.3962783813477</v>
       </c>
     </row>
     <row r="11">
@@ -841,7 +841,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>123.5384521484375</v>
+        <v>123.235954284668</v>
       </c>
     </row>
     <row r="12">
@@ -878,7 +878,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>125.0911712646484</v>
+        <v>125.0619049072266</v>
       </c>
     </row>
     <row r="13">
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>126.1494293212891</v>
+        <v>126.3288192749023</v>
       </c>
     </row>
     <row r="14">
@@ -952,7 +952,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>124.5844955444336</v>
+        <v>124.5384216308594</v>
       </c>
     </row>
     <row r="15">
@@ -989,7 +989,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>123.5412750244141</v>
+        <v>123.4311676025391</v>
       </c>
     </row>
     <row r="16">
@@ -1026,7 +1026,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>121.3753433227539</v>
+        <v>121.6108093261719</v>
       </c>
     </row>
     <row r="17">
@@ -1063,7 +1063,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>120.9937286376953</v>
+        <v>120.9695816040039</v>
       </c>
     </row>
     <row r="18">
@@ -1100,7 +1100,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>120.3768539428711</v>
+        <v>120.5356521606445</v>
       </c>
     </row>
     <row r="19">
@@ -1137,7 +1137,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>120.1741027832031</v>
+        <v>120.1792297363281</v>
       </c>
     </row>
     <row r="20">

--- a/src/models/prediction/one_day_output.xlsx
+++ b/src/models/prediction/one_day_output.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\ML_project\Bargh_ML\src\models\prediction\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{993385EB-6D15-425C-8C60-E9A748FCA5EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14055B2F-9528-418A-A0F3-2E952901C4E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,10 +34,10 @@
     <t>hour</t>
   </si>
   <si>
-    <t>temp_sens</t>
+    <t>prediction</t>
   </si>
   <si>
-    <t>prediction</t>
+    <t>prediction_turbo</t>
   </si>
   <si>
     <t>پرند</t>
@@ -417,9 +417,8 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="4" width="18.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
@@ -453,16 +452,16 @@
         <v>7</v>
       </c>
       <c r="D2" s="2">
-        <v>45943</v>
+        <v>46012</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
       <c r="F2">
-        <v>20</v>
+        <v>161.92813724221759</v>
       </c>
       <c r="G2">
-        <v>134.56498718261719</v>
+        <v>161.92813724221759</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
@@ -476,16 +475,16 @@
         <v>7</v>
       </c>
       <c r="D3" s="2">
-        <v>45943</v>
+        <v>46012</v>
       </c>
       <c r="E3">
         <v>2</v>
       </c>
       <c r="F3">
-        <v>20</v>
+        <v>162.27356178048001</v>
       </c>
       <c r="G3">
-        <v>134.56498718261719</v>
+        <v>162.27356178048001</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -499,16 +498,16 @@
         <v>7</v>
       </c>
       <c r="D4" s="2">
-        <v>45943</v>
+        <v>46012</v>
       </c>
       <c r="E4">
         <v>3</v>
       </c>
       <c r="F4">
-        <v>20</v>
+        <v>162.489452278812</v>
       </c>
       <c r="G4">
-        <v>134.56498718261719</v>
+        <v>162.489452278812</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -522,16 +521,16 @@
         <v>7</v>
       </c>
       <c r="D5" s="2">
-        <v>45943</v>
+        <v>46012</v>
       </c>
       <c r="E5">
         <v>4</v>
       </c>
       <c r="F5">
-        <v>20</v>
+        <v>162.6189867505235</v>
       </c>
       <c r="G5">
-        <v>134.89642333984381</v>
+        <v>162.6189867505235</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -545,16 +544,16 @@
         <v>7</v>
       </c>
       <c r="D6" s="2">
-        <v>45943</v>
+        <v>46012</v>
       </c>
       <c r="E6">
         <v>5</v>
       </c>
       <c r="F6">
-        <v>20</v>
+        <v>162.79169914918899</v>
       </c>
       <c r="G6">
-        <v>136.1460876464844</v>
+        <v>162.79169914918899</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
@@ -568,16 +567,16 @@
         <v>7</v>
       </c>
       <c r="D7" s="2">
-        <v>45943</v>
+        <v>46012</v>
       </c>
       <c r="E7">
         <v>6</v>
       </c>
       <c r="F7">
-        <v>20</v>
+        <v>163.007589647521</v>
       </c>
       <c r="G7">
-        <v>135.81465148925781</v>
+        <v>163.007589647521</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
@@ -591,16 +590,16 @@
         <v>7</v>
       </c>
       <c r="D8" s="2">
-        <v>45943</v>
+        <v>46012</v>
       </c>
       <c r="E8">
         <v>7</v>
       </c>
       <c r="F8">
-        <v>20</v>
+        <v>163.1371237738077</v>
       </c>
       <c r="G8">
-        <v>135.81465148925781</v>
+        <v>163.1371237738077</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
@@ -614,16 +613,16 @@
         <v>7</v>
       </c>
       <c r="D9" s="2">
-        <v>45943</v>
+        <v>46012</v>
       </c>
       <c r="E9">
         <v>8</v>
       </c>
       <c r="F9">
-        <v>20</v>
+        <v>163.2234801458529</v>
       </c>
       <c r="G9">
-        <v>135.81465148925781</v>
+        <v>163.2234801458529</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
@@ -637,16 +636,16 @@
         <v>7</v>
       </c>
       <c r="D10" s="2">
-        <v>45943</v>
+        <v>46012</v>
       </c>
       <c r="E10">
         <v>9</v>
       </c>
       <c r="F10">
-        <v>20</v>
+        <v>162.27356178048001</v>
       </c>
       <c r="G10">
-        <v>135.78480529785159</v>
+        <v>162.27356178048001</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
@@ -660,16 +659,16 @@
         <v>7</v>
       </c>
       <c r="D11" s="2">
-        <v>45943</v>
+        <v>46012</v>
       </c>
       <c r="E11">
         <v>10</v>
       </c>
       <c r="F11">
-        <v>20</v>
+        <v>159.46698551805551</v>
       </c>
       <c r="G11">
-        <v>127.3347930908203</v>
+        <v>159.46698551805551</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
@@ -683,16 +682,16 @@
         <v>7</v>
       </c>
       <c r="D12" s="2">
-        <v>45943</v>
+        <v>46012</v>
       </c>
       <c r="E12">
         <v>11</v>
       </c>
       <c r="F12">
-        <v>20</v>
+        <v>157.178546192559</v>
       </c>
       <c r="G12">
-        <v>129.43402099609381</v>
+        <v>157.178546192559</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
@@ -706,16 +705,16 @@
         <v>7</v>
       </c>
       <c r="D13" s="2">
-        <v>45943</v>
+        <v>46012</v>
       </c>
       <c r="E13">
         <v>12</v>
       </c>
       <c r="F13">
-        <v>20</v>
+        <v>155.23553170757171</v>
       </c>
       <c r="G13">
-        <v>129.193603515625</v>
+        <v>155.23553170757171</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
@@ -729,16 +728,16 @@
         <v>7</v>
       </c>
       <c r="D14" s="2">
-        <v>45943</v>
+        <v>46012</v>
       </c>
       <c r="E14">
         <v>13</v>
       </c>
       <c r="F14">
-        <v>20</v>
+        <v>153.7242982192482</v>
       </c>
       <c r="G14">
-        <v>126.58229064941411</v>
+        <v>153.7242982192482</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
@@ -752,16 +751,16 @@
         <v>7</v>
       </c>
       <c r="D15" s="2">
-        <v>45943</v>
+        <v>46012</v>
       </c>
       <c r="E15">
         <v>14</v>
       </c>
       <c r="F15">
-        <v>20</v>
+        <v>152.81755726269219</v>
       </c>
       <c r="G15">
-        <v>125.5184860229492</v>
+        <v>152.81755726269219</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
@@ -775,16 +774,16 @@
         <v>7</v>
       </c>
       <c r="D16" s="2">
-        <v>45943</v>
+        <v>46012</v>
       </c>
       <c r="E16">
         <v>15</v>
       </c>
       <c r="F16">
-        <v>20</v>
+        <v>152.51531142858951</v>
       </c>
       <c r="G16">
-        <v>124.66026306152339</v>
+        <v>152.51531142858951</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
@@ -798,16 +797,16 @@
         <v>7</v>
       </c>
       <c r="D17" s="2">
-        <v>45943</v>
+        <v>46012</v>
       </c>
       <c r="E17">
         <v>16</v>
       </c>
       <c r="F17">
-        <v>20</v>
+        <v>152.68802382725499</v>
       </c>
       <c r="G17">
-        <v>124.427375793457</v>
+        <v>152.68802382725499</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
@@ -821,16 +820,16 @@
         <v>7</v>
       </c>
       <c r="D18" s="2">
-        <v>45943</v>
+        <v>46012</v>
       </c>
       <c r="E18">
         <v>17</v>
       </c>
       <c r="F18">
-        <v>20</v>
+        <v>153.5084077209163</v>
       </c>
       <c r="G18">
-        <v>125.5184860229492</v>
+        <v>153.5084077209163</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
@@ -844,16 +843,16 @@
         <v>7</v>
       </c>
       <c r="D19" s="2">
-        <v>45943</v>
+        <v>46012</v>
       </c>
       <c r="E19">
         <v>18</v>
       </c>
       <c r="F19">
-        <v>20</v>
+        <v>155.0628193089062</v>
       </c>
       <c r="G19">
-        <v>125.2504806518555</v>
+        <v>155.0628193089062</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
@@ -867,16 +866,16 @@
         <v>7</v>
       </c>
       <c r="D20" s="2">
-        <v>45943</v>
+        <v>46012</v>
       </c>
       <c r="E20">
         <v>19</v>
       </c>
       <c r="F20">
-        <v>20</v>
+        <v>156.0559157739454</v>
       </c>
       <c r="G20">
-        <v>127.73374176025391</v>
+        <v>156.0559157739454</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
@@ -890,16 +889,16 @@
         <v>7</v>
       </c>
       <c r="D21" s="2">
-        <v>45943</v>
+        <v>46012</v>
       </c>
       <c r="E21">
         <v>20</v>
       </c>
       <c r="F21">
-        <v>20</v>
+        <v>156.78994329556161</v>
       </c>
       <c r="G21">
-        <v>128.74815368652341</v>
+        <v>156.78994329556161</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
@@ -913,16 +912,16 @@
         <v>7</v>
       </c>
       <c r="D22" s="2">
-        <v>45943</v>
+        <v>46012</v>
       </c>
       <c r="E22">
         <v>21</v>
       </c>
       <c r="F22">
-        <v>20</v>
+        <v>157.09218982051391</v>
       </c>
       <c r="G22">
-        <v>132.63435363769531</v>
+        <v>157.09218982051391</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
@@ -936,16 +935,16 @@
         <v>7</v>
       </c>
       <c r="D23" s="2">
-        <v>45943</v>
+        <v>46012</v>
       </c>
       <c r="E23">
         <v>22</v>
       </c>
       <c r="F23">
-        <v>20</v>
+        <v>157.95575181384149</v>
       </c>
       <c r="G23">
-        <v>134.3412780761719</v>
+        <v>157.95575181384149</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
@@ -959,16 +958,16 @@
         <v>7</v>
       </c>
       <c r="D24" s="2">
-        <v>45943</v>
+        <v>46012</v>
       </c>
       <c r="E24">
         <v>23</v>
       </c>
       <c r="F24">
-        <v>20</v>
+        <v>159.1647387772127</v>
       </c>
       <c r="G24">
-        <v>134.80181884765619</v>
+        <v>159.1647387772127</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
@@ -982,16 +981,16 @@
         <v>7</v>
       </c>
       <c r="D25" s="2">
-        <v>45943</v>
+        <v>46012</v>
       </c>
       <c r="E25">
         <v>24</v>
       </c>
       <c r="F25">
-        <v>20</v>
+        <v>160.33054746302369</v>
       </c>
       <c r="G25">
-        <v>135.33349609375</v>
+        <v>160.33054746302369</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
@@ -1005,16 +1004,16 @@
         <v>8</v>
       </c>
       <c r="D26" s="2">
-        <v>45943</v>
+        <v>46012</v>
       </c>
       <c r="E26">
         <v>1</v>
       </c>
       <c r="F26">
-        <v>20</v>
+        <v>157.7628195059894</v>
       </c>
       <c r="G26">
-        <v>137.26136779785159</v>
+        <v>157.7628195059894</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
@@ -1028,16 +1027,16 @@
         <v>8</v>
       </c>
       <c r="D27" s="2">
-        <v>45943</v>
+        <v>46012</v>
       </c>
       <c r="E27">
         <v>2</v>
       </c>
       <c r="F27">
-        <v>20</v>
+        <v>158.08939877874721</v>
       </c>
       <c r="G27">
-        <v>137.26136779785159</v>
+        <v>158.08939877874721</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
@@ -1051,16 +1050,16 @@
         <v>8</v>
       </c>
       <c r="D28" s="2">
-        <v>45943</v>
+        <v>46012</v>
       </c>
       <c r="E28">
         <v>3</v>
       </c>
       <c r="F28">
-        <v>20</v>
+        <v>158.293510977305</v>
       </c>
       <c r="G28">
-        <v>137.26136779785159</v>
+        <v>158.293510977305</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
@@ -1074,16 +1073,16 @@
         <v>8</v>
       </c>
       <c r="D29" s="2">
-        <v>45943</v>
+        <v>46012</v>
       </c>
       <c r="E29">
         <v>4</v>
       </c>
       <c r="F29">
-        <v>20</v>
+        <v>158.41597845972939</v>
       </c>
       <c r="G29">
-        <v>136.4103698730469</v>
+        <v>158.41597845972939</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
@@ -1097,16 +1096,16 @@
         <v>8</v>
       </c>
       <c r="D30" s="2">
-        <v>45943</v>
+        <v>46012</v>
       </c>
       <c r="E30">
         <v>5</v>
       </c>
       <c r="F30">
-        <v>20</v>
+        <v>158.57926821857561</v>
       </c>
       <c r="G30">
-        <v>136.4103698730469</v>
+        <v>158.57926821857561</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
@@ -1120,16 +1119,16 @@
         <v>8</v>
       </c>
       <c r="D31" s="2">
-        <v>45943</v>
+        <v>46012</v>
       </c>
       <c r="E31">
         <v>6</v>
       </c>
       <c r="F31">
-        <v>20</v>
+        <v>158.7833804171334</v>
       </c>
       <c r="G31">
-        <v>137.26136779785159</v>
+        <v>158.7833804171334</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
@@ -1143,16 +1142,16 @@
         <v>8</v>
       </c>
       <c r="D32" s="2">
-        <v>45943</v>
+        <v>46012</v>
       </c>
       <c r="E32">
         <v>7</v>
       </c>
       <c r="F32">
-        <v>20</v>
+        <v>158.9058475729783</v>
       </c>
       <c r="G32">
-        <v>136.4103698730469</v>
+        <v>158.9058475729783</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
@@ -1166,16 +1165,16 @@
         <v>8</v>
       </c>
       <c r="D33" s="2">
-        <v>45943</v>
+        <v>46012</v>
       </c>
       <c r="E33">
         <v>8</v>
       </c>
       <c r="F33">
-        <v>20</v>
+        <v>158.9874926156912</v>
       </c>
       <c r="G33">
-        <v>137.26136779785159</v>
+        <v>158.9874926156912</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
@@ -1189,16 +1188,16 @@
         <v>8</v>
       </c>
       <c r="D34" s="2">
-        <v>45943</v>
+        <v>46012</v>
       </c>
       <c r="E34">
         <v>9</v>
       </c>
       <c r="F34">
-        <v>20</v>
+        <v>158.08939877874721</v>
       </c>
       <c r="G34">
-        <v>137.34666442871091</v>
+        <v>158.08939877874721</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
@@ -1212,16 +1211,16 @@
         <v>8</v>
       </c>
       <c r="D35" s="2">
-        <v>45943</v>
+        <v>46012</v>
       </c>
       <c r="E35">
         <v>10</v>
       </c>
       <c r="F35">
-        <v>20</v>
+        <v>155.43594040160829</v>
       </c>
       <c r="G35">
-        <v>137.07875061035159</v>
+        <v>155.43594040160829</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
@@ -1235,16 +1234,16 @@
         <v>8</v>
       </c>
       <c r="D36" s="2">
-        <v>45943</v>
+        <v>46012</v>
       </c>
       <c r="E36">
         <v>11</v>
       </c>
       <c r="F36">
-        <v>20</v>
+        <v>153.2723510560734</v>
       </c>
       <c r="G36">
-        <v>135.5482482910156</v>
+        <v>153.2723510560734</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
@@ -1258,16 +1257,16 @@
         <v>8</v>
       </c>
       <c r="D37" s="2">
-        <v>45943</v>
+        <v>46012</v>
       </c>
       <c r="E37">
         <v>12</v>
       </c>
       <c r="F37">
-        <v>20</v>
+        <v>151.4353412690534</v>
       </c>
       <c r="G37">
-        <v>132.88124084472659</v>
+        <v>151.4353412690534</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
@@ -1281,16 +1280,16 @@
         <v>8</v>
       </c>
       <c r="D38" s="2">
-        <v>45943</v>
+        <v>46012</v>
       </c>
       <c r="E38">
         <v>13</v>
       </c>
       <c r="F38">
-        <v>20</v>
+        <v>150.006555879149</v>
       </c>
       <c r="G38">
-        <v>132.49810791015619</v>
+        <v>150.006555879149</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
@@ -1304,16 +1303,16 @@
         <v>8</v>
       </c>
       <c r="D39" s="2">
-        <v>45943</v>
+        <v>46012</v>
       </c>
       <c r="E39">
         <v>14</v>
       </c>
       <c r="F39">
-        <v>20</v>
+        <v>149.14928382875749</v>
       </c>
       <c r="G39">
-        <v>131.2583312988281</v>
+        <v>149.14928382875749</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
@@ -1327,16 +1326,16 @@
         <v>8</v>
       </c>
       <c r="D40" s="2">
-        <v>45943</v>
+        <v>46012</v>
       </c>
       <c r="E40">
         <v>15</v>
       </c>
       <c r="F40">
-        <v>20</v>
+        <v>148.86352756722539</v>
       </c>
       <c r="G40">
-        <v>130.63336181640619</v>
+        <v>148.86352756722539</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
@@ -1350,16 +1349,16 @@
         <v>8</v>
       </c>
       <c r="D41" s="2">
-        <v>45943</v>
+        <v>46012</v>
       </c>
       <c r="E41">
         <v>16</v>
       </c>
       <c r="F41">
-        <v>20</v>
+        <v>149.02681732607161</v>
       </c>
       <c r="G41">
-        <v>129.98399353027341</v>
+        <v>149.02681732607161</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
@@ -1373,16 +1372,16 @@
         <v>8</v>
       </c>
       <c r="D42" s="2">
-        <v>45943</v>
+        <v>46012</v>
       </c>
       <c r="E42">
         <v>17</v>
       </c>
       <c r="F42">
-        <v>20</v>
+        <v>149.80244368059121</v>
       </c>
       <c r="G42">
-        <v>130.17430114746091</v>
+        <v>149.80244368059121</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
@@ -1396,16 +1395,16 @@
         <v>8</v>
       </c>
       <c r="D43" s="2">
-        <v>45943</v>
+        <v>46012</v>
       </c>
       <c r="E43">
         <v>18</v>
       </c>
       <c r="F43">
-        <v>20</v>
+        <v>151.27205151020721</v>
       </c>
       <c r="G43">
-        <v>132.6360778808594</v>
+        <v>151.27205151020721</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
@@ -1419,16 +1418,16 @@
         <v>8</v>
       </c>
       <c r="D44" s="2">
-        <v>45943</v>
+        <v>46012</v>
       </c>
       <c r="E44">
         <v>19</v>
       </c>
       <c r="F44">
-        <v>20</v>
+        <v>152.21096778686271</v>
       </c>
       <c r="G44">
-        <v>134.69371032714841</v>
+        <v>152.21096778686271</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
@@ -1442,16 +1441,16 @@
         <v>8</v>
       </c>
       <c r="D45" s="2">
-        <v>45943</v>
+        <v>46012</v>
       </c>
       <c r="E45">
         <v>20</v>
       </c>
       <c r="F45">
-        <v>20</v>
+        <v>152.90494909866939</v>
       </c>
       <c r="G45">
-        <v>135.440185546875</v>
+        <v>152.90494909866939</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
@@ -1465,16 +1464,16 @@
         <v>8</v>
       </c>
       <c r="D46" s="2">
-        <v>45943</v>
+        <v>46012</v>
       </c>
       <c r="E46">
         <v>21</v>
       </c>
       <c r="F46">
-        <v>20</v>
+        <v>153.19070601336051</v>
       </c>
       <c r="G46">
-        <v>136.50816345214841</v>
+        <v>153.19070601336051</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
@@ -1488,16 +1487,16 @@
         <v>8</v>
       </c>
       <c r="D47" s="2">
-        <v>45943</v>
+        <v>46012</v>
       </c>
       <c r="E47">
         <v>22</v>
       </c>
       <c r="F47">
-        <v>20</v>
+        <v>154.00715480759169</v>
       </c>
       <c r="G47">
-        <v>137.3591613769531</v>
+        <v>154.00715480759169</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
@@ -1511,16 +1510,16 @@
         <v>8</v>
       </c>
       <c r="D48" s="2">
-        <v>45943</v>
+        <v>46012</v>
       </c>
       <c r="E48">
         <v>23</v>
       </c>
       <c r="F48">
-        <v>20</v>
+        <v>155.15018328280499</v>
       </c>
       <c r="G48">
-        <v>137.01237487792969</v>
+        <v>155.15018328280499</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
@@ -1534,16 +1533,16 @@
         <v>8</v>
       </c>
       <c r="D49" s="2">
-        <v>45943</v>
+        <v>46012</v>
       </c>
       <c r="E49">
         <v>24</v>
       </c>
       <c r="F49">
-        <v>20</v>
+        <v>156.25238915011829</v>
       </c>
       <c r="G49">
-        <v>136.36334228515619</v>
+        <v>156.25238915011829</v>
       </c>
     </row>
   </sheetData>

--- a/src/models/prediction/one_day_output.xlsx
+++ b/src/models/prediction/one_day_output.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F49"/>
+  <dimension ref="A1:G49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,6 +458,11 @@
           <t>prediction</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>prediction_turbo</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -465,7 +470,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>پرند</t>
+          <t>قم</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -480,7 +485,10 @@
         <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>162.3834140215662</v>
+        <v>117.4620455041235</v>
+      </c>
+      <c r="G2" t="n">
+        <v>72.02131557775978</v>
       </c>
     </row>
     <row r="3">
@@ -504,8 +512,9 @@
         <v>2</v>
       </c>
       <c r="F3" t="n">
-        <v>162.6933260694623</v>
-      </c>
+        <v>162.6933260717041</v>
+      </c>
+      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
@@ -528,8 +537,9 @@
         <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>162.8870212446688</v>
-      </c>
+        <v>162.8870212469538</v>
+      </c>
+      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
@@ -552,8 +562,9 @@
         <v>4</v>
       </c>
       <c r="F5" t="n">
-        <v>163.0032385047488</v>
-      </c>
+        <v>163.0032385070598</v>
+      </c>
+      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
@@ -576,8 +587,9 @@
         <v>5</v>
       </c>
       <c r="F6" t="n">
-        <v>163.158194644914</v>
-      </c>
+        <v>163.1581946472595</v>
+      </c>
+      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
@@ -600,8 +612,9 @@
         <v>6</v>
       </c>
       <c r="F7" t="n">
-        <v>163.3518898201205</v>
-      </c>
+        <v>163.3518898225092</v>
+      </c>
+      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
@@ -624,8 +637,9 @@
         <v>7</v>
       </c>
       <c r="F8" t="n">
-        <v>163.4681067702882</v>
-      </c>
+        <v>163.4681067727029</v>
+      </c>
+      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
@@ -648,8 +662,9 @@
         <v>8</v>
       </c>
       <c r="F9" t="n">
-        <v>163.545584995327</v>
-      </c>
+        <v>163.545584997759</v>
+      </c>
+      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
@@ -672,8 +687,9 @@
         <v>9</v>
       </c>
       <c r="F10" t="n">
-        <v>162.6933260694623</v>
-      </c>
+        <v>162.6933260717041</v>
+      </c>
+      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
@@ -696,8 +712,9 @@
         <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>160.1752889854732</v>
-      </c>
+        <v>160.1752889871531</v>
+      </c>
+      <c r="G11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
@@ -720,8 +737,9 @@
         <v>11</v>
       </c>
       <c r="F12" t="n">
-        <v>158.1221200895455</v>
-      </c>
+        <v>158.1221200907671</v>
+      </c>
+      <c r="G12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
@@ -744,8 +762,9 @@
         <v>12</v>
       </c>
       <c r="F13" t="n">
-        <v>156.3788635126872</v>
-      </c>
+        <v>156.3788635135197</v>
+      </c>
+      <c r="G13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
@@ -768,8 +787,9 @@
         <v>13</v>
       </c>
       <c r="F14" t="n">
-        <v>155.0229972862418</v>
-      </c>
+        <v>155.0229972867718</v>
+      </c>
+      <c r="G14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
@@ -792,8 +812,9 @@
         <v>14</v>
       </c>
       <c r="F15" t="n">
-        <v>154.2094767755939</v>
-      </c>
+        <v>154.2094767759423</v>
+      </c>
+      <c r="G15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
@@ -816,8 +837,9 @@
         <v>15</v>
       </c>
       <c r="F16" t="n">
-        <v>153.9383043050855</v>
-      </c>
+        <v>153.9383043053734</v>
+      </c>
+      <c r="G16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
@@ -840,8 +862,9 @@
         <v>16</v>
       </c>
       <c r="F17" t="n">
-        <v>154.0932604452507</v>
-      </c>
+        <v>154.0932604455732</v>
+      </c>
+      <c r="G17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
@@ -864,8 +887,9 @@
         <v>17</v>
       </c>
       <c r="F18" t="n">
-        <v>154.8293021110353</v>
-      </c>
+        <v>154.8293021115221</v>
+      </c>
+      <c r="G18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
@@ -888,8 +912,9 @@
         <v>18</v>
       </c>
       <c r="F19" t="n">
-        <v>156.223907372522</v>
-      </c>
+        <v>156.22390737332</v>
+      </c>
+      <c r="G19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
@@ -912,8 +937,9 @@
         <v>19</v>
       </c>
       <c r="F20" t="n">
-        <v>157.1149053334279</v>
-      </c>
+        <v>157.1149053344248</v>
+      </c>
+      <c r="G20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
@@ -936,8 +962,9 @@
         <v>20</v>
       </c>
       <c r="F21" t="n">
-        <v>157.7734687741738</v>
-      </c>
+        <v>157.7734687753177</v>
+      </c>
+      <c r="G21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
@@ -960,8 +987,9 @@
         <v>21</v>
       </c>
       <c r="F22" t="n">
-        <v>158.0446418645068</v>
-      </c>
+        <v>158.0446418657111</v>
+      </c>
+      <c r="G22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
@@ -984,8 +1012,9 @@
         <v>22</v>
       </c>
       <c r="F23" t="n">
-        <v>158.8194225653327</v>
-      </c>
+        <v>158.8194225667099</v>
+      </c>
+      <c r="G23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
@@ -1008,8 +1037,9 @@
         <v>23</v>
       </c>
       <c r="F24" t="n">
-        <v>159.9041157014451</v>
-      </c>
+        <v>159.9041157030644</v>
+      </c>
+      <c r="G24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
@@ -1032,8 +1062,9 @@
         <v>24</v>
       </c>
       <c r="F25" t="n">
-        <v>160.9500696429114</v>
-      </c>
+        <v>160.9500696447642</v>
+      </c>
+      <c r="G25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
@@ -1058,6 +1089,7 @@
       <c r="F26" t="n">
         <v>159.724073041235</v>
       </c>
+      <c r="G26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
@@ -1082,6 +1114,7 @@
       <c r="F27" t="n">
         <v>160.0584281068797</v>
       </c>
+      <c r="G27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
@@ -1106,6 +1139,7 @@
       <c r="F28" t="n">
         <v>160.2674001796367</v>
       </c>
+      <c r="G28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
@@ -1130,6 +1164,7 @@
       <c r="F29" t="n">
         <v>160.3927835904686</v>
       </c>
+      <c r="G29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
@@ -1154,6 +1189,7 @@
       <c r="F30" t="n">
         <v>160.5599612486741</v>
       </c>
+      <c r="G30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
@@ -1178,6 +1214,7 @@
       <c r="F31" t="n">
         <v>160.7689333214311</v>
       </c>
+      <c r="G31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
@@ -1202,6 +1239,7 @@
       <c r="F32" t="n">
         <v>160.8943163979077</v>
       </c>
+      <c r="G32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
@@ -1226,6 +1264,7 @@
       <c r="F33" t="n">
         <v>160.9779053941881</v>
       </c>
+      <c r="G33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
@@ -1250,6 +1289,7 @@
       <c r="F34" t="n">
         <v>160.0584281068797</v>
       </c>
+      <c r="G34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
@@ -1274,6 +1314,7 @@
       <c r="F35" t="n">
         <v>157.341791370011</v>
       </c>
+      <c r="G35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
@@ -1298,6 +1339,7 @@
       <c r="F36" t="n">
         <v>155.1266873569926</v>
       </c>
+      <c r="G36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
@@ -1322,6 +1364,7 @@
       <c r="F37" t="n">
         <v>153.2459387021798</v>
       </c>
+      <c r="G37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
@@ -1346,6 +1389,7 @@
       <c r="F38" t="n">
         <v>151.7831341928809</v>
       </c>
+      <c r="G38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
@@ -1370,6 +1414,7 @@
       <c r="F39" t="n">
         <v>150.9054506514133</v>
       </c>
+      <c r="G39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
@@ -1394,6 +1439,7 @@
       <c r="F40" t="n">
         <v>150.6128905854418</v>
       </c>
+      <c r="G40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
@@ -1418,6 +1464,7 @@
       <c r="F41" t="n">
         <v>150.7800682436474</v>
       </c>
+      <c r="G41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
@@ -1442,6 +1489,7 @@
       <c r="F42" t="n">
         <v>151.5741621201239</v>
       </c>
+      <c r="G42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
@@ -1466,6 +1514,7 @@
       <c r="F43" t="n">
         <v>153.0787610439742</v>
       </c>
+      <c r="G43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
@@ -1490,6 +1539,7 @@
       <c r="F44" t="n">
         <v>154.040032745834</v>
       </c>
+      <c r="G44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
@@ -1514,6 +1564,7 @@
       <c r="F45" t="n">
         <v>154.7505376260301</v>
       </c>
+      <c r="G45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
@@ -1538,6 +1589,7 @@
       <c r="F46" t="n">
         <v>155.0430983607122</v>
       </c>
+      <c r="G46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
@@ -1562,6 +1614,7 @@
       <c r="F47" t="n">
         <v>155.8789866517401</v>
       </c>
+      <c r="G47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
@@ -1586,6 +1639,7 @@
       <c r="F48" t="n">
         <v>157.0492304263568</v>
       </c>
+      <c r="G48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
@@ -1610,6 +1664,7 @@
       <c r="F49" t="n">
         <v>158.1776796142292</v>
       </c>
+      <c r="G49" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/src/models/prediction/one_day_output.xlsx
+++ b/src/models/prediction/one_day_output.xlsx
@@ -16,10 +16,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -58,12 +55,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,36 +425,46 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G49"/>
+  <dimension ref="A1:I49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>code</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>hour</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>temperature</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>prediction</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>prediction_turbo</t>
         </is>
@@ -468,1203 +474,1587 @@
       <c r="A2" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>قم</t>
-        </is>
+      <c r="B2" t="n">
+        <v>149</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>G11</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="n">
-        <v>46012</v>
-      </c>
-      <c r="E2" t="n">
+          <t>سیکل ترکیبی قم</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>G11</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>1404/11/11</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
         <v>1</v>
       </c>
-      <c r="F2" t="n">
-        <v>117.4620455041235</v>
-      </c>
       <c r="G2" t="n">
-        <v>72.02131557775978</v>
+        <v>25</v>
+      </c>
+      <c r="H2" t="n">
+        <v>102.87</v>
+      </c>
+      <c r="I2" t="n">
+        <v>102.44</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>پرند</t>
-        </is>
+      <c r="B3" t="n">
+        <v>104</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>G11</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="n">
-        <v>46012</v>
-      </c>
-      <c r="E3" t="n">
+          <t>پرند</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>G11</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>1404/11/11</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
         <v>2</v>
       </c>
-      <c r="F3" t="n">
-        <v>162.6933260717041</v>
-      </c>
-      <c r="G3" t="inlineStr"/>
+      <c r="G3" t="n">
+        <v>35</v>
+      </c>
+      <c r="H3" t="n">
+        <v>133.29</v>
+      </c>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>پرند</t>
-        </is>
+      <c r="B4" t="n">
+        <v>104</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>G11</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>46012</v>
-      </c>
-      <c r="E4" t="n">
+          <t>پرند</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>G11</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>1404/11/11</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
         <v>3</v>
       </c>
-      <c r="F4" t="n">
-        <v>162.8870212469538</v>
-      </c>
-      <c r="G4" t="inlineStr"/>
+      <c r="G4" t="n">
+        <v>35</v>
+      </c>
+      <c r="H4" t="n">
+        <v>133.29</v>
+      </c>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>پرند</t>
-        </is>
+      <c r="B5" t="n">
+        <v>104</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>G11</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>46012</v>
-      </c>
-      <c r="E5" t="n">
+          <t>پرند</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>G11</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>1404/11/11</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
         <v>4</v>
       </c>
-      <c r="F5" t="n">
-        <v>163.0032385070598</v>
-      </c>
-      <c r="G5" t="inlineStr"/>
+      <c r="G5" t="n">
+        <v>35</v>
+      </c>
+      <c r="H5" t="n">
+        <v>133.29</v>
+      </c>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>پرند</t>
-        </is>
+      <c r="B6" t="n">
+        <v>104</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>G11</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="n">
-        <v>46012</v>
-      </c>
-      <c r="E6" t="n">
+          <t>پرند</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>G11</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>1404/11/11</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
         <v>5</v>
       </c>
-      <c r="F6" t="n">
-        <v>163.1581946472595</v>
-      </c>
-      <c r="G6" t="inlineStr"/>
+      <c r="G6" t="n">
+        <v>35</v>
+      </c>
+      <c r="H6" t="n">
+        <v>133.29</v>
+      </c>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>پرند</t>
-        </is>
+      <c r="B7" t="n">
+        <v>104</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>G11</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="n">
-        <v>46012</v>
-      </c>
-      <c r="E7" t="n">
+          <t>پرند</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>G11</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>1404/11/11</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
         <v>6</v>
       </c>
-      <c r="F7" t="n">
-        <v>163.3518898225092</v>
-      </c>
-      <c r="G7" t="inlineStr"/>
+      <c r="G7" t="n">
+        <v>35</v>
+      </c>
+      <c r="H7" t="n">
+        <v>133.29</v>
+      </c>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>پرند</t>
-        </is>
+      <c r="B8" t="n">
+        <v>104</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>G11</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="n">
-        <v>46012</v>
-      </c>
-      <c r="E8" t="n">
+          <t>پرند</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>G11</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>1404/11/11</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
         <v>7</v>
       </c>
-      <c r="F8" t="n">
-        <v>163.4681067727029</v>
-      </c>
-      <c r="G8" t="inlineStr"/>
+      <c r="G8" t="n">
+        <v>35</v>
+      </c>
+      <c r="H8" t="n">
+        <v>133.29</v>
+      </c>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>پرند</t>
-        </is>
+      <c r="B9" t="n">
+        <v>104</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>G11</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>46012</v>
-      </c>
-      <c r="E9" t="n">
+          <t>پرند</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>G11</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>1404/11/11</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
         <v>8</v>
       </c>
-      <c r="F9" t="n">
-        <v>163.545584997759</v>
-      </c>
-      <c r="G9" t="inlineStr"/>
+      <c r="G9" t="n">
+        <v>35</v>
+      </c>
+      <c r="H9" t="n">
+        <v>133.29</v>
+      </c>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>پرند</t>
-        </is>
+      <c r="B10" t="n">
+        <v>104</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>G11</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="n">
-        <v>46012</v>
-      </c>
-      <c r="E10" t="n">
+          <t>پرند</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>G11</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>1404/11/11</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
         <v>9</v>
       </c>
-      <c r="F10" t="n">
-        <v>162.6933260717041</v>
-      </c>
-      <c r="G10" t="inlineStr"/>
+      <c r="G10" t="n">
+        <v>35</v>
+      </c>
+      <c r="H10" t="n">
+        <v>133.29</v>
+      </c>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>پرند</t>
-        </is>
+      <c r="B11" t="n">
+        <v>104</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>G11</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="n">
-        <v>46012</v>
-      </c>
-      <c r="E11" t="n">
+          <t>پرند</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>G11</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>1404/11/11</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
         <v>10</v>
       </c>
-      <c r="F11" t="n">
-        <v>160.1752889871531</v>
-      </c>
-      <c r="G11" t="inlineStr"/>
+      <c r="G11" t="n">
+        <v>35</v>
+      </c>
+      <c r="H11" t="n">
+        <v>133.29</v>
+      </c>
+      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>پرند</t>
-        </is>
+      <c r="B12" t="n">
+        <v>104</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>G11</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="n">
-        <v>46012</v>
-      </c>
-      <c r="E12" t="n">
+          <t>پرند</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>G11</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>1404/11/11</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
         <v>11</v>
       </c>
-      <c r="F12" t="n">
-        <v>158.1221200907671</v>
-      </c>
-      <c r="G12" t="inlineStr"/>
+      <c r="G12" t="n">
+        <v>35</v>
+      </c>
+      <c r="H12" t="n">
+        <v>133.29</v>
+      </c>
+      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>پرند</t>
-        </is>
+      <c r="B13" t="n">
+        <v>104</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>G11</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="n">
-        <v>46012</v>
-      </c>
-      <c r="E13" t="n">
+          <t>پرند</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>G11</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>1404/11/11</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
         <v>12</v>
       </c>
-      <c r="F13" t="n">
-        <v>156.3788635135197</v>
-      </c>
-      <c r="G13" t="inlineStr"/>
+      <c r="G13" t="n">
+        <v>35</v>
+      </c>
+      <c r="H13" t="n">
+        <v>133.29</v>
+      </c>
+      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>پرند</t>
-        </is>
+      <c r="B14" t="n">
+        <v>104</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>G11</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="n">
-        <v>46012</v>
-      </c>
-      <c r="E14" t="n">
+          <t>پرند</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>G11</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>1404/11/11</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
         <v>13</v>
       </c>
-      <c r="F14" t="n">
-        <v>155.0229972867718</v>
-      </c>
-      <c r="G14" t="inlineStr"/>
+      <c r="G14" t="n">
+        <v>35</v>
+      </c>
+      <c r="H14" t="n">
+        <v>133.29</v>
+      </c>
+      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>پرند</t>
-        </is>
+      <c r="B15" t="n">
+        <v>104</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>G11</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="n">
-        <v>46012</v>
-      </c>
-      <c r="E15" t="n">
+          <t>پرند</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>G11</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>1404/11/11</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
         <v>14</v>
       </c>
-      <c r="F15" t="n">
-        <v>154.2094767759423</v>
-      </c>
-      <c r="G15" t="inlineStr"/>
+      <c r="G15" t="n">
+        <v>35</v>
+      </c>
+      <c r="H15" t="n">
+        <v>133.29</v>
+      </c>
+      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>پرند</t>
-        </is>
+      <c r="B16" t="n">
+        <v>104</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>G11</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="n">
-        <v>46012</v>
-      </c>
-      <c r="E16" t="n">
+          <t>پرند</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>G11</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>1404/11/11</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
         <v>15</v>
       </c>
-      <c r="F16" t="n">
-        <v>153.9383043053734</v>
-      </c>
-      <c r="G16" t="inlineStr"/>
+      <c r="G16" t="n">
+        <v>35</v>
+      </c>
+      <c r="H16" t="n">
+        <v>133.29</v>
+      </c>
+      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>پرند</t>
-        </is>
+      <c r="B17" t="n">
+        <v>104</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>G11</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="n">
-        <v>46012</v>
-      </c>
-      <c r="E17" t="n">
+          <t>پرند</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>G11</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>1404/11/11</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
         <v>16</v>
       </c>
-      <c r="F17" t="n">
-        <v>154.0932604455732</v>
-      </c>
-      <c r="G17" t="inlineStr"/>
+      <c r="G17" t="n">
+        <v>35</v>
+      </c>
+      <c r="H17" t="n">
+        <v>133.29</v>
+      </c>
+      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>پرند</t>
-        </is>
+      <c r="B18" t="n">
+        <v>104</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>G11</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="n">
-        <v>46012</v>
-      </c>
-      <c r="E18" t="n">
+          <t>پرند</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>G11</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>1404/11/11</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
         <v>17</v>
       </c>
-      <c r="F18" t="n">
-        <v>154.8293021115221</v>
-      </c>
-      <c r="G18" t="inlineStr"/>
+      <c r="G18" t="n">
+        <v>35</v>
+      </c>
+      <c r="H18" t="n">
+        <v>133.29</v>
+      </c>
+      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>پرند</t>
-        </is>
+      <c r="B19" t="n">
+        <v>104</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>G11</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="n">
-        <v>46012</v>
-      </c>
-      <c r="E19" t="n">
+          <t>پرند</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>G11</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>1404/11/11</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
         <v>18</v>
       </c>
-      <c r="F19" t="n">
-        <v>156.22390737332</v>
-      </c>
-      <c r="G19" t="inlineStr"/>
+      <c r="G19" t="n">
+        <v>35</v>
+      </c>
+      <c r="H19" t="n">
+        <v>133.29</v>
+      </c>
+      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>پرند</t>
-        </is>
+      <c r="B20" t="n">
+        <v>104</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>G11</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="n">
-        <v>46012</v>
-      </c>
-      <c r="E20" t="n">
+          <t>پرند</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>G11</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>1404/11/11</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
         <v>19</v>
       </c>
-      <c r="F20" t="n">
-        <v>157.1149053344248</v>
-      </c>
-      <c r="G20" t="inlineStr"/>
+      <c r="G20" t="n">
+        <v>35</v>
+      </c>
+      <c r="H20" t="n">
+        <v>133.29</v>
+      </c>
+      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>پرند</t>
-        </is>
+      <c r="B21" t="n">
+        <v>104</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>G11</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="n">
-        <v>46012</v>
-      </c>
-      <c r="E21" t="n">
+          <t>پرند</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>G11</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>1404/11/11</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
         <v>20</v>
       </c>
-      <c r="F21" t="n">
-        <v>157.7734687753177</v>
-      </c>
-      <c r="G21" t="inlineStr"/>
+      <c r="G21" t="n">
+        <v>35</v>
+      </c>
+      <c r="H21" t="n">
+        <v>133.29</v>
+      </c>
+      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>پرند</t>
-        </is>
+      <c r="B22" t="n">
+        <v>104</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>G11</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="n">
-        <v>46012</v>
-      </c>
-      <c r="E22" t="n">
+          <t>پرند</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>G11</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>1404/11/11</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
         <v>21</v>
       </c>
-      <c r="F22" t="n">
-        <v>158.0446418657111</v>
-      </c>
-      <c r="G22" t="inlineStr"/>
+      <c r="G22" t="n">
+        <v>35</v>
+      </c>
+      <c r="H22" t="n">
+        <v>133.29</v>
+      </c>
+      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>پرند</t>
-        </is>
+      <c r="B23" t="n">
+        <v>104</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>G11</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="n">
-        <v>46012</v>
-      </c>
-      <c r="E23" t="n">
+          <t>پرند</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>G11</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>1404/11/11</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
         <v>22</v>
       </c>
-      <c r="F23" t="n">
-        <v>158.8194225667099</v>
-      </c>
-      <c r="G23" t="inlineStr"/>
+      <c r="G23" t="n">
+        <v>35</v>
+      </c>
+      <c r="H23" t="n">
+        <v>133.29</v>
+      </c>
+      <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
         <v>22</v>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>پرند</t>
-        </is>
+      <c r="B24" t="n">
+        <v>104</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>G11</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="n">
-        <v>46012</v>
-      </c>
-      <c r="E24" t="n">
+          <t>پرند</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>G11</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>1404/11/11</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
         <v>23</v>
       </c>
-      <c r="F24" t="n">
-        <v>159.9041157030644</v>
-      </c>
-      <c r="G24" t="inlineStr"/>
+      <c r="G24" t="n">
+        <v>35</v>
+      </c>
+      <c r="H24" t="n">
+        <v>133.29</v>
+      </c>
+      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>پرند</t>
-        </is>
+      <c r="B25" t="n">
+        <v>104</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>G11</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="n">
-        <v>46012</v>
-      </c>
-      <c r="E25" t="n">
+          <t>پرند</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>G11</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>1404/11/11</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
         <v>24</v>
       </c>
-      <c r="F25" t="n">
-        <v>160.9500696447642</v>
-      </c>
-      <c r="G25" t="inlineStr"/>
+      <c r="G25" t="n">
+        <v>35</v>
+      </c>
+      <c r="H25" t="n">
+        <v>133.29</v>
+      </c>
+      <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>پرند</t>
-        </is>
+      <c r="B26" t="n">
+        <v>104</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>G12</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="n">
-        <v>46012</v>
-      </c>
-      <c r="E26" t="n">
+          <t>پرند</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>G12</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>1404/11/11</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
         <v>1</v>
       </c>
-      <c r="F26" t="n">
-        <v>159.724073041235</v>
-      </c>
-      <c r="G26" t="inlineStr"/>
+      <c r="G26" t="n">
+        <v>35</v>
+      </c>
+      <c r="H26" t="n">
+        <v>128.91</v>
+      </c>
+      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>پرند</t>
-        </is>
+      <c r="B27" t="n">
+        <v>104</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>G12</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="n">
-        <v>46012</v>
-      </c>
-      <c r="E27" t="n">
+          <t>پرند</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>G12</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>1404/11/11</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
         <v>2</v>
       </c>
-      <c r="F27" t="n">
-        <v>160.0584281068797</v>
-      </c>
-      <c r="G27" t="inlineStr"/>
+      <c r="G27" t="n">
+        <v>35</v>
+      </c>
+      <c r="H27" t="n">
+        <v>128.91</v>
+      </c>
+      <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
         <v>26</v>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>پرند</t>
-        </is>
+      <c r="B28" t="n">
+        <v>104</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>G12</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="n">
-        <v>46012</v>
-      </c>
-      <c r="E28" t="n">
+          <t>پرند</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>G12</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>1404/11/11</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
         <v>3</v>
       </c>
-      <c r="F28" t="n">
-        <v>160.2674001796367</v>
-      </c>
-      <c r="G28" t="inlineStr"/>
+      <c r="G28" t="n">
+        <v>35</v>
+      </c>
+      <c r="H28" t="n">
+        <v>128.91</v>
+      </c>
+      <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
         <v>27</v>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>پرند</t>
-        </is>
+      <c r="B29" t="n">
+        <v>104</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>G12</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="n">
-        <v>46012</v>
-      </c>
-      <c r="E29" t="n">
+          <t>پرند</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>G12</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>1404/11/11</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
         <v>4</v>
       </c>
-      <c r="F29" t="n">
-        <v>160.3927835904686</v>
-      </c>
-      <c r="G29" t="inlineStr"/>
+      <c r="G29" t="n">
+        <v>35</v>
+      </c>
+      <c r="H29" t="n">
+        <v>128.91</v>
+      </c>
+      <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
         <v>28</v>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>پرند</t>
-        </is>
+      <c r="B30" t="n">
+        <v>104</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>G12</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="n">
-        <v>46012</v>
-      </c>
-      <c r="E30" t="n">
+          <t>پرند</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>G12</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>1404/11/11</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
         <v>5</v>
       </c>
-      <c r="F30" t="n">
-        <v>160.5599612486741</v>
-      </c>
-      <c r="G30" t="inlineStr"/>
+      <c r="G30" t="n">
+        <v>35</v>
+      </c>
+      <c r="H30" t="n">
+        <v>128.91</v>
+      </c>
+      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
         <v>29</v>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>پرند</t>
-        </is>
+      <c r="B31" t="n">
+        <v>104</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>G12</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="n">
-        <v>46012</v>
-      </c>
-      <c r="E31" t="n">
+          <t>پرند</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>G12</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>1404/11/11</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
         <v>6</v>
       </c>
-      <c r="F31" t="n">
-        <v>160.7689333214311</v>
-      </c>
-      <c r="G31" t="inlineStr"/>
+      <c r="G31" t="n">
+        <v>35</v>
+      </c>
+      <c r="H31" t="n">
+        <v>128.91</v>
+      </c>
+      <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>پرند</t>
-        </is>
+      <c r="B32" t="n">
+        <v>104</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>G12</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="n">
-        <v>46012</v>
-      </c>
-      <c r="E32" t="n">
+          <t>پرند</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>G12</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>1404/11/11</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
         <v>7</v>
       </c>
-      <c r="F32" t="n">
-        <v>160.8943163979077</v>
-      </c>
-      <c r="G32" t="inlineStr"/>
+      <c r="G32" t="n">
+        <v>35</v>
+      </c>
+      <c r="H32" t="n">
+        <v>128.91</v>
+      </c>
+      <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
         <v>31</v>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>پرند</t>
-        </is>
+      <c r="B33" t="n">
+        <v>104</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>G12</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="n">
-        <v>46012</v>
-      </c>
-      <c r="E33" t="n">
+          <t>پرند</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>G12</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>1404/11/11</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
         <v>8</v>
       </c>
-      <c r="F33" t="n">
-        <v>160.9779053941881</v>
-      </c>
-      <c r="G33" t="inlineStr"/>
+      <c r="G33" t="n">
+        <v>35</v>
+      </c>
+      <c r="H33" t="n">
+        <v>128.91</v>
+      </c>
+      <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
         <v>32</v>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>پرند</t>
-        </is>
+      <c r="B34" t="n">
+        <v>104</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>G12</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="n">
-        <v>46012</v>
-      </c>
-      <c r="E34" t="n">
+          <t>پرند</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>G12</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>1404/11/11</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
         <v>9</v>
       </c>
-      <c r="F34" t="n">
-        <v>160.0584281068797</v>
-      </c>
-      <c r="G34" t="inlineStr"/>
+      <c r="G34" t="n">
+        <v>35</v>
+      </c>
+      <c r="H34" t="n">
+        <v>128.91</v>
+      </c>
+      <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
         <v>33</v>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>پرند</t>
-        </is>
+      <c r="B35" t="n">
+        <v>104</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>G12</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="n">
-        <v>46012</v>
-      </c>
-      <c r="E35" t="n">
+          <t>پرند</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>G12</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>1404/11/11</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
         <v>10</v>
       </c>
-      <c r="F35" t="n">
-        <v>157.341791370011</v>
-      </c>
-      <c r="G35" t="inlineStr"/>
+      <c r="G35" t="n">
+        <v>35</v>
+      </c>
+      <c r="H35" t="n">
+        <v>128.91</v>
+      </c>
+      <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
         <v>34</v>
       </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>پرند</t>
-        </is>
+      <c r="B36" t="n">
+        <v>104</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>G12</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="n">
-        <v>46012</v>
-      </c>
-      <c r="E36" t="n">
+          <t>پرند</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>G12</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>1404/11/11</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
         <v>11</v>
       </c>
-      <c r="F36" t="n">
-        <v>155.1266873569926</v>
-      </c>
-      <c r="G36" t="inlineStr"/>
+      <c r="G36" t="n">
+        <v>35</v>
+      </c>
+      <c r="H36" t="n">
+        <v>128.91</v>
+      </c>
+      <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
         <v>35</v>
       </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>پرند</t>
-        </is>
+      <c r="B37" t="n">
+        <v>104</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>G12</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="n">
-        <v>46012</v>
-      </c>
-      <c r="E37" t="n">
+          <t>پرند</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>G12</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>1404/11/11</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
         <v>12</v>
       </c>
-      <c r="F37" t="n">
-        <v>153.2459387021798</v>
-      </c>
-      <c r="G37" t="inlineStr"/>
+      <c r="G37" t="n">
+        <v>35</v>
+      </c>
+      <c r="H37" t="n">
+        <v>128.91</v>
+      </c>
+      <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
         <v>36</v>
       </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>پرند</t>
-        </is>
+      <c r="B38" t="n">
+        <v>104</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>G12</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="n">
-        <v>46012</v>
-      </c>
-      <c r="E38" t="n">
+          <t>پرند</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>G12</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>1404/11/11</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
         <v>13</v>
       </c>
-      <c r="F38" t="n">
-        <v>151.7831341928809</v>
-      </c>
-      <c r="G38" t="inlineStr"/>
+      <c r="G38" t="n">
+        <v>35</v>
+      </c>
+      <c r="H38" t="n">
+        <v>128.91</v>
+      </c>
+      <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
         <v>37</v>
       </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>پرند</t>
-        </is>
+      <c r="B39" t="n">
+        <v>104</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>G12</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="n">
-        <v>46012</v>
-      </c>
-      <c r="E39" t="n">
+          <t>پرند</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>G12</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>1404/11/11</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
         <v>14</v>
       </c>
-      <c r="F39" t="n">
-        <v>150.9054506514133</v>
-      </c>
-      <c r="G39" t="inlineStr"/>
+      <c r="G39" t="n">
+        <v>35</v>
+      </c>
+      <c r="H39" t="n">
+        <v>128.91</v>
+      </c>
+      <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
         <v>38</v>
       </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>پرند</t>
-        </is>
+      <c r="B40" t="n">
+        <v>104</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>G12</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="n">
-        <v>46012</v>
-      </c>
-      <c r="E40" t="n">
+          <t>پرند</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>G12</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>1404/11/11</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
         <v>15</v>
       </c>
-      <c r="F40" t="n">
-        <v>150.6128905854418</v>
-      </c>
-      <c r="G40" t="inlineStr"/>
+      <c r="G40" t="n">
+        <v>35</v>
+      </c>
+      <c r="H40" t="n">
+        <v>128.91</v>
+      </c>
+      <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
         <v>39</v>
       </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>پرند</t>
-        </is>
+      <c r="B41" t="n">
+        <v>104</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>G12</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="n">
-        <v>46012</v>
-      </c>
-      <c r="E41" t="n">
+          <t>پرند</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>G12</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>1404/11/11</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
         <v>16</v>
       </c>
-      <c r="F41" t="n">
-        <v>150.7800682436474</v>
-      </c>
-      <c r="G41" t="inlineStr"/>
+      <c r="G41" t="n">
+        <v>35</v>
+      </c>
+      <c r="H41" t="n">
+        <v>128.91</v>
+      </c>
+      <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
         <v>40</v>
       </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>پرند</t>
-        </is>
+      <c r="B42" t="n">
+        <v>104</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>G12</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="n">
-        <v>46012</v>
-      </c>
-      <c r="E42" t="n">
+          <t>پرند</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>G12</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>1404/11/11</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
         <v>17</v>
       </c>
-      <c r="F42" t="n">
-        <v>151.5741621201239</v>
-      </c>
-      <c r="G42" t="inlineStr"/>
+      <c r="G42" t="n">
+        <v>35</v>
+      </c>
+      <c r="H42" t="n">
+        <v>128.91</v>
+      </c>
+      <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
         <v>41</v>
       </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>پرند</t>
-        </is>
+      <c r="B43" t="n">
+        <v>104</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>G12</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="n">
-        <v>46012</v>
-      </c>
-      <c r="E43" t="n">
+          <t>پرند</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>G12</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>1404/11/11</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
         <v>18</v>
       </c>
-      <c r="F43" t="n">
-        <v>153.0787610439742</v>
-      </c>
-      <c r="G43" t="inlineStr"/>
+      <c r="G43" t="n">
+        <v>35</v>
+      </c>
+      <c r="H43" t="n">
+        <v>128.91</v>
+      </c>
+      <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
         <v>42</v>
       </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>پرند</t>
-        </is>
+      <c r="B44" t="n">
+        <v>104</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>G12</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="n">
-        <v>46012</v>
-      </c>
-      <c r="E44" t="n">
+          <t>پرند</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>G12</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>1404/11/11</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
         <v>19</v>
       </c>
-      <c r="F44" t="n">
-        <v>154.040032745834</v>
-      </c>
-      <c r="G44" t="inlineStr"/>
+      <c r="G44" t="n">
+        <v>35</v>
+      </c>
+      <c r="H44" t="n">
+        <v>128.91</v>
+      </c>
+      <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
         <v>43</v>
       </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>پرند</t>
-        </is>
+      <c r="B45" t="n">
+        <v>104</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>G12</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="n">
-        <v>46012</v>
-      </c>
-      <c r="E45" t="n">
+          <t>پرند</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>G12</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>1404/11/11</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
         <v>20</v>
       </c>
-      <c r="F45" t="n">
-        <v>154.7505376260301</v>
-      </c>
-      <c r="G45" t="inlineStr"/>
+      <c r="G45" t="n">
+        <v>35</v>
+      </c>
+      <c r="H45" t="n">
+        <v>128.91</v>
+      </c>
+      <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
         <v>44</v>
       </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>پرند</t>
-        </is>
+      <c r="B46" t="n">
+        <v>104</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>G12</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="n">
-        <v>46012</v>
-      </c>
-      <c r="E46" t="n">
+          <t>پرند</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>G12</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>1404/11/11</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
         <v>21</v>
       </c>
-      <c r="F46" t="n">
-        <v>155.0430983607122</v>
-      </c>
-      <c r="G46" t="inlineStr"/>
+      <c r="G46" t="n">
+        <v>35</v>
+      </c>
+      <c r="H46" t="n">
+        <v>128.91</v>
+      </c>
+      <c r="I46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
         <v>45</v>
       </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>پرند</t>
-        </is>
+      <c r="B47" t="n">
+        <v>104</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>G12</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="n">
-        <v>46012</v>
-      </c>
-      <c r="E47" t="n">
+          <t>پرند</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>G12</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>1404/11/11</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
         <v>22</v>
       </c>
-      <c r="F47" t="n">
-        <v>155.8789866517401</v>
-      </c>
-      <c r="G47" t="inlineStr"/>
+      <c r="G47" t="n">
+        <v>35</v>
+      </c>
+      <c r="H47" t="n">
+        <v>128.91</v>
+      </c>
+      <c r="I47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
         <v>46</v>
       </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>پرند</t>
-        </is>
+      <c r="B48" t="n">
+        <v>104</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>G12</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="n">
-        <v>46012</v>
-      </c>
-      <c r="E48" t="n">
+          <t>پرند</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>G12</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>1404/11/11</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
         <v>23</v>
       </c>
-      <c r="F48" t="n">
-        <v>157.0492304263568</v>
-      </c>
-      <c r="G48" t="inlineStr"/>
+      <c r="G48" t="n">
+        <v>24</v>
+      </c>
+      <c r="H48" t="n">
+        <v>138.1</v>
+      </c>
+      <c r="I48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
         <v>47</v>
       </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>پرند</t>
-        </is>
+      <c r="B49" t="n">
+        <v>104</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>G12</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="n">
-        <v>46012</v>
-      </c>
-      <c r="E49" t="n">
+          <t>پرند</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>G12</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>1404/11/11</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
         <v>24</v>
       </c>
-      <c r="F49" t="n">
-        <v>158.1776796142292</v>
-      </c>
-      <c r="G49" t="inlineStr"/>
+      <c r="G49" t="n">
+        <v>24</v>
+      </c>
+      <c r="H49" t="n">
+        <v>138.1</v>
+      </c>
+      <c r="I49" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
